--- a/pensum/ma05/MA05_Markedssegmentering_Regneark_Kundelonnsomhet.xlsx
+++ b/pensum/ma05/MA05_Markedssegmentering_Regneark_Kundelonnsomhet.xlsx
@@ -1057,7 +1057,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1220,6 +1220,10 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1521,7 +1525,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -1532,7 +1536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1554,7 +1558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -1565,7 +1569,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>13</v>
       </c>
@@ -1633,7 +1637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>24</v>
       </c>
@@ -1931,8 +1935,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row ht="27" customHeight="true" r="33" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A33" t="s">
         <v>80</v>
       </c>
       <c r="B33" s="21" t="s">
@@ -1942,8 +1946,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
+    <row ht="27" customHeight="true" r="34" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A34" t="s">
         <v>83</v>
       </c>
       <c r="B34" s="21" t="s">
@@ -1975,8 +1979,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
+    <row ht="27" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A37" t="s">
         <v>89</v>
       </c>
       <c r="B37" s="21" t="s">
@@ -3138,8 +3142,8 @@
         <v>185</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row ht="27" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A24" t="s">
         <v>186</v>
       </c>
       <c r="B24" s="36" t="str">
@@ -3151,8 +3155,8 @@
         <v>1525.44616937661</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+    <row ht="27" customHeight="true" r="25" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A25" t="s">
         <v>187</v>
       </c>
       <c r="B25" s="36" t="str">
@@ -3640,8 +3644,8 @@
         <v>5184</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="19" t="s">
+    <row ht="27" customHeight="true" r="47" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="41" r="A47" t="s">
         <v>240</v>
       </c>
       <c r="B47" s="33" t="n">
